--- a/artfynd/A 24801-2026 artfynd.xlsx
+++ b/artfynd/A 24801-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135106253</v>
+        <v>135110592</v>
       </c>
       <c r="B3" t="n">
-        <v>96783</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673081</v>
+        <v>672981</v>
       </c>
       <c r="R3" t="n">
-        <v>6556246</v>
+        <v>6556419</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135106451</v>
+        <v>135110861</v>
       </c>
       <c r="B4" t="n">
-        <v>96783</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängshagen, Ängshagen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673080</v>
+        <v>672820</v>
       </c>
       <c r="R4" t="n">
-        <v>6556230</v>
+        <v>6556471</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,19 +937,9 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135106958</v>
+        <v>135106253</v>
       </c>
       <c r="B5" t="n">
         <v>96783</v>
@@ -1011,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>673087</v>
+        <v>673081</v>
       </c>
       <c r="R5" t="n">
-        <v>6556259</v>
+        <v>6556246</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135108141</v>
+        <v>135106451</v>
       </c>
       <c r="B6" t="n">
         <v>96783</v>
@@ -1108,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>673014</v>
+        <v>673080</v>
       </c>
       <c r="R6" t="n">
-        <v>6556297</v>
+        <v>6556230</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1143,7 +1133,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1153,7 +1143,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134873285</v>
+        <v>135106958</v>
       </c>
       <c r="B7" t="n">
-        <v>96410</v>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,37 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2812</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mensättraskogen, Ådalen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>673158</v>
+        <v>673087</v>
       </c>
       <c r="R7" t="n">
-        <v>6556244</v>
+        <v>6556259</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,12 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135106078</v>
+        <v>135108141</v>
       </c>
       <c r="B8" t="n">
-        <v>96533</v>
+        <v>96783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,37 +1278,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ängshagen, Ängshagen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>673111</v>
+        <v>673014</v>
       </c>
       <c r="R8" t="n">
-        <v>6556240</v>
+        <v>6556297</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1345,9 +1335,19 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,22 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134873997</v>
+        <v>135110495</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
+        <v>96783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,37 +1385,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ådalen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673164</v>
+        <v>672952</v>
       </c>
       <c r="R9" t="n">
-        <v>6556268</v>
+        <v>6556482</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,12 +1439,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Liten kudde</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134875838</v>
+        <v>135111384</v>
       </c>
       <c r="B10" t="n">
-        <v>91937</v>
+        <v>96783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,37 +1487,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673158</v>
+        <v>672883</v>
       </c>
       <c r="R10" t="n">
-        <v>6556328</v>
+        <v>6556559</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1541,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stora kuddar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,48 +1578,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135107587</v>
+        <v>135113394</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>96783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673040</v>
+        <v>673100</v>
       </c>
       <c r="R11" t="n">
-        <v>6556279</v>
+        <v>6556258</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1641,34 +1655,40 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett flertal tuvor.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134874101</v>
+        <v>135113440</v>
       </c>
       <c r="B12" t="n">
-        <v>81031</v>
+        <v>96783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1696,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6444</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673164</v>
+        <v>673090</v>
       </c>
       <c r="R12" t="n">
-        <v>6556268</v>
+        <v>6556260</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,17 +1754,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På hassel.</t>
+          <t>Ett flertal tuvor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1749,66 +1773,71 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135107231</v>
+        <v>135114482</v>
       </c>
       <c r="B13" t="n">
-        <v>79130</v>
+        <v>96783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>673059</v>
+        <v>672967</v>
       </c>
       <c r="R13" t="n">
-        <v>6556263</v>
+        <v>6556484</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1840,77 +1869,73 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal stubbe.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135109852</v>
+        <v>134873285</v>
       </c>
       <c r="B14" t="n">
-        <v>79130</v>
+        <v>96410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>2812</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Mensättraskogen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673014</v>
+        <v>673158</v>
       </c>
       <c r="R14" t="n">
-        <v>6556440</v>
+        <v>6556244</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1934,17 +1959,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På bark på gammal tall .</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,48 +1991,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135110213</v>
+        <v>135106078</v>
       </c>
       <c r="B15" t="n">
-        <v>79130</v>
+        <v>96533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673039</v>
+        <v>673111</v>
       </c>
       <c r="R15" t="n">
-        <v>6556463</v>
+        <v>6556240</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2039,19 +2059,9 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2066,65 +2076,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134875457</v>
+        <v>135111442</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>91995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ängshagen, Ängshagen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>673171</v>
+        <v>672918</v>
       </c>
       <c r="R16" t="n">
-        <v>6556308</v>
+        <v>6556591</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2148,17 +2162,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2173,22 +2192,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135107091</v>
+        <v>134873997</v>
       </c>
       <c r="B17" t="n">
-        <v>4776</v>
+        <v>91937</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,39 +2215,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>673060</v>
+        <v>673164</v>
       </c>
       <c r="R17" t="n">
-        <v>6556270</v>
+        <v>6556268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,12 +2269,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135109941</v>
+        <v>134875838</v>
       </c>
       <c r="B18" t="n">
-        <v>5181</v>
+        <v>91937</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,42 +2312,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>673014</v>
+        <v>673158</v>
       </c>
       <c r="R18" t="n">
-        <v>6556440</v>
+        <v>6556328</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2357,12 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,10 +2398,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134879122</v>
+        <v>135110590</v>
       </c>
       <c r="B19" t="n">
-        <v>44182</v>
+        <v>91937</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2400,42 +2409,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>673138</v>
+        <v>672969</v>
       </c>
       <c r="R19" t="n">
-        <v>6556268</v>
+        <v>6556454</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2459,12 +2463,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2479,22 +2493,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134875172</v>
+        <v>135111223</v>
       </c>
       <c r="B20" t="n">
-        <v>4782</v>
+        <v>91937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,42 +2516,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>673170</v>
+        <v>672820</v>
       </c>
       <c r="R20" t="n">
-        <v>6556304</v>
+        <v>6556471</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2561,12 +2570,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,53 +2602,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134877363</v>
+        <v>135107587</v>
       </c>
       <c r="B21" t="n">
-        <v>4782</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673056</v>
+        <v>673040</v>
       </c>
       <c r="R21" t="n">
-        <v>6556413</v>
+        <v>6556279</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2663,12 +2667,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,10 +2699,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134878316</v>
+        <v>134874101</v>
       </c>
       <c r="B22" t="n">
-        <v>4782</v>
+        <v>81031</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,42 +2710,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>6444</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673107</v>
+        <v>673164</v>
       </c>
       <c r="R22" t="n">
-        <v>6556321</v>
+        <v>6556268</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2775,7 +2774,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På hassel.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,10 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134876582</v>
+        <v>135107231</v>
       </c>
       <c r="B23" t="n">
-        <v>58136</v>
+        <v>79130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,46 +2812,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>673118</v>
+        <v>673059</v>
       </c>
       <c r="R23" t="n">
-        <v>6556347</v>
+        <v>6556263</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2876,12 +2866,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal stubbe.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2908,57 +2903,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134876782</v>
+        <v>135109852</v>
       </c>
       <c r="B24" t="n">
-        <v>58131</v>
+        <v>79130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103023</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>673118</v>
+        <v>673014</v>
       </c>
       <c r="R24" t="n">
-        <v>6556347</v>
+        <v>6556440</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2982,12 +2968,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På bark på gammal tall .</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3014,53 +3005,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135109471</v>
+        <v>135110213</v>
       </c>
       <c r="B25" t="n">
-        <v>58131</v>
+        <v>79130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103023</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>673071</v>
+        <v>673039</v>
       </c>
       <c r="R25" t="n">
-        <v>6556479</v>
+        <v>6556463</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3087,9 +3073,19 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3104,22 +3100,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134873311</v>
+        <v>134875457</v>
       </c>
       <c r="B26" t="n">
-        <v>5201</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3127,16 +3123,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3147,22 +3143,22 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mensättraskogen, Ådalen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>673158</v>
+        <v>673171</v>
       </c>
       <c r="R26" t="n">
-        <v>6556244</v>
+        <v>6556308</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3192,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3218,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135106795</v>
+        <v>135113520</v>
       </c>
       <c r="B27" t="n">
-        <v>5201</v>
+        <v>56915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3229,16 +3230,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>100088</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3246,25 +3247,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ängshagen, Ängshagen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>673082</v>
+        <v>673098</v>
       </c>
       <c r="R27" t="n">
-        <v>6556254</v>
+        <v>6556272</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3291,49 +3296,40 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135106133</v>
+        <v>135107091</v>
       </c>
       <c r="B28" t="n">
-        <v>8449</v>
+        <v>4776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3341,21 +3337,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3370,13 +3366,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>673112</v>
+        <v>673060</v>
       </c>
       <c r="R28" t="n">
-        <v>6556248</v>
+        <v>6556270</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3432,10 +3428,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134877169</v>
+        <v>135109941</v>
       </c>
       <c r="B29" t="n">
-        <v>99112</v>
+        <v>5181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3443,34 +3439,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>673051</v>
+        <v>673014</v>
       </c>
       <c r="R29" t="n">
-        <v>6556425</v>
+        <v>6556440</v>
       </c>
       <c r="S29" t="n">
         <v>7</v>
@@ -3497,12 +3498,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3529,42 +3530,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134877712</v>
+        <v>134879122</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>44182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3573,13 +3570,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>673077</v>
+        <v>673138</v>
       </c>
       <c r="R30" t="n">
-        <v>6556440</v>
+        <v>6556268</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3635,57 +3632,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134877853</v>
+        <v>135114115</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>44182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>673077</v>
+        <v>673018</v>
       </c>
       <c r="R31" t="n">
-        <v>6556446</v>
+        <v>6556301</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3709,12 +3706,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På murken björklåga, 1 st. kläckhål ca 8 cm från en fnöskticka! Puppskalet satt kvar i kläckhålet.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3723,21 +3725,1592 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134875172</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>673170</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6556304</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134877363</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>673056</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6556413</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134878316</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>673107</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6556321</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134876582</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>673118</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6556347</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134876782</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>673118</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6556347</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135109471</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>673071</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6556479</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134873311</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mensättraskogen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>673158</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6556244</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135106795</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ängshagen, Ängshagen, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>673082</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6556254</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135111905</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>672990</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6556541</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135106133</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>673112</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6556248</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135114337</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ålsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>673007</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6556457</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134877169</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>673051</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6556425</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134877712</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>673077</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6556440</v>
+      </c>
+      <c r="S44" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134877853</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ådalen, Ådalen, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>673077</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6556446</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135113719</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ålsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>673027</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6556383</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ca 15 plantor.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24801-2026 artfynd.xlsx
+++ b/artfynd/A 24801-2026 artfynd.xlsx
@@ -4296,11 +4296,14 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
@@ -4343,6 +4346,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ett par med flera ungar.</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 24801-2026 artfynd.xlsx
+++ b/artfynd/A 24801-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134873285</v>
+        <v>135106078</v>
       </c>
       <c r="B14" t="n">
-        <v>96410</v>
+        <v>96533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2812</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mensättraskogen, Ådalen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>673158</v>
+        <v>673111</v>
       </c>
       <c r="R14" t="n">
-        <v>6556244</v>
+        <v>6556240</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,48 +1991,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135106078</v>
+        <v>135111442</v>
       </c>
       <c r="B15" t="n">
-        <v>96533</v>
+        <v>91995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ängshagen, Ängshagen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>673111</v>
+        <v>672918</v>
       </c>
       <c r="R15" t="n">
-        <v>6556240</v>
+        <v>6556591</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2059,9 +2068,19 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,69 +2095,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135111442</v>
+        <v>134873997</v>
       </c>
       <c r="B16" t="n">
-        <v>91995</v>
+        <v>91937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ängshagen, Ängshagen, Srm</t>
+          <t>Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672918</v>
+        <v>673164</v>
       </c>
       <c r="R16" t="n">
-        <v>6556591</v>
+        <v>6556268</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2162,22 +2172,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2192,19 +2192,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134873997</v>
+        <v>134875838</v>
       </c>
       <c r="B17" t="n">
         <v>91937</v>
@@ -2235,17 +2235,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ådalen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>673164</v>
+        <v>673158</v>
       </c>
       <c r="R17" t="n">
-        <v>6556268</v>
+        <v>6556328</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134875838</v>
+        <v>135110590</v>
       </c>
       <c r="B18" t="n">
         <v>91937</v>
@@ -2332,17 +2332,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>673158</v>
+        <v>672969</v>
       </c>
       <c r="R18" t="n">
-        <v>6556328</v>
+        <v>6556454</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2366,12 +2366,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2386,19 +2396,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135110590</v>
+        <v>135111223</v>
       </c>
       <c r="B19" t="n">
         <v>91937</v>
@@ -2429,17 +2439,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672969</v>
+        <v>672820</v>
       </c>
       <c r="R19" t="n">
-        <v>6556454</v>
+        <v>6556471</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2466,19 +2476,9 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2493,44 +2493,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135111223</v>
+        <v>135107587</v>
       </c>
       <c r="B20" t="n">
-        <v>91937</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,13 +2540,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672820</v>
+        <v>673040</v>
       </c>
       <c r="R20" t="n">
-        <v>6556471</v>
+        <v>6556279</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2602,48 +2602,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135107587</v>
+        <v>134874101</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>81031</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6444</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>673040</v>
+        <v>673164</v>
       </c>
       <c r="R21" t="n">
-        <v>6556279</v>
+        <v>6556268</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2667,12 +2667,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På hassel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2699,48 +2704,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134874101</v>
+        <v>135107231</v>
       </c>
       <c r="B22" t="n">
-        <v>81031</v>
+        <v>79130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6444</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skriftlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Graphis scripta</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ådalen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>673164</v>
+        <v>673059</v>
       </c>
       <c r="R22" t="n">
-        <v>6556268</v>
+        <v>6556263</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2764,17 +2769,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På hassel.</t>
+          <t>På gammal stubbe.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2801,7 +2806,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135107231</v>
+        <v>135109852</v>
       </c>
       <c r="B23" t="n">
         <v>79130</v>
@@ -2836,13 +2841,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>673059</v>
+        <v>673014</v>
       </c>
       <c r="R23" t="n">
-        <v>6556263</v>
+        <v>6556440</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2876,7 +2881,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal stubbe.</t>
+          <t>På bark på gammal tall .</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2903,7 +2908,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135109852</v>
+        <v>135110213</v>
       </c>
       <c r="B24" t="n">
         <v>79130</v>
@@ -2934,17 +2939,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>673014</v>
+        <v>673039</v>
       </c>
       <c r="R24" t="n">
-        <v>6556440</v>
+        <v>6556463</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2971,14 +2976,19 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På bark på gammal tall .</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2993,60 +3003,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135110213</v>
+        <v>134875457</v>
       </c>
       <c r="B25" t="n">
-        <v>79130</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>673039</v>
+        <v>673171</v>
       </c>
       <c r="R25" t="n">
-        <v>6556463</v>
+        <v>6556308</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3070,22 +3085,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackmärken i död gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,22 +3110,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134875457</v>
+        <v>135113520</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>56915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,16 +3133,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100088</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3140,25 +3150,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>673171</v>
+        <v>673098</v>
       </c>
       <c r="R26" t="n">
-        <v>6556308</v>
+        <v>6556272</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3182,17 +3196,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hackmärken i död gran.</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3201,28 +3210,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135113520</v>
+        <v>135107091</v>
       </c>
       <c r="B27" t="n">
-        <v>56915</v>
+        <v>4776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,43 +3240,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100088</v>
+        <v>100299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ålsta, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>673098</v>
+        <v>673060</v>
       </c>
       <c r="R27" t="n">
-        <v>6556272</v>
+        <v>6556270</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3307,29 +3313,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135107091</v>
+        <v>135109941</v>
       </c>
       <c r="B28" t="n">
-        <v>4776</v>
+        <v>5181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3337,27 +3342,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3366,13 +3371,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>673060</v>
+        <v>673014</v>
       </c>
       <c r="R28" t="n">
-        <v>6556270</v>
+        <v>6556440</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3428,10 +3433,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135109941</v>
+        <v>134879122</v>
       </c>
       <c r="B29" t="n">
-        <v>5181</v>
+        <v>44182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,27 +3444,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3468,13 +3473,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>673014</v>
+        <v>673138</v>
       </c>
       <c r="R29" t="n">
-        <v>6556440</v>
+        <v>6556268</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3498,12 +3503,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3530,7 +3535,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134879122</v>
+        <v>135114115</v>
       </c>
       <c r="B30" t="n">
         <v>44182</v>
@@ -3558,22 +3563,26 @@
           <t>(Fabricius, 1794)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>673138</v>
+        <v>673018</v>
       </c>
       <c r="R30" t="n">
-        <v>6556268</v>
+        <v>6556301</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,12 +3609,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På murken björklåga, 1 st. kläckhål ca 8 cm från en fnöskticka! Puppskalet satt kvar i kläckhålet.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3614,28 +3628,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135114115</v>
+        <v>134875172</v>
       </c>
       <c r="B31" t="n">
-        <v>44182</v>
+        <v>4782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,43 +3658,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101735</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålsta, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>673018</v>
+        <v>673170</v>
       </c>
       <c r="R31" t="n">
-        <v>6556301</v>
+        <v>6556304</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3706,17 +3717,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På murken björklåga, 1 st. kläckhål ca 8 cm från en fnöskticka! Puppskalet satt kvar i kläckhålet.</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3725,26 +3731,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134875172</v>
+        <v>134877363</v>
       </c>
       <c r="B32" t="n">
         <v>4782</v>
@@ -3784,13 +3789,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>673170</v>
+        <v>673056</v>
       </c>
       <c r="R32" t="n">
-        <v>6556304</v>
+        <v>6556413</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3846,7 +3851,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134877363</v>
+        <v>134878316</v>
       </c>
       <c r="B33" t="n">
         <v>4782</v>
@@ -3886,10 +3891,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>673056</v>
+        <v>673107</v>
       </c>
       <c r="R33" t="n">
-        <v>6556413</v>
+        <v>6556321</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -3922,6 +3927,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3948,10 +3958,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134878316</v>
+        <v>134876782</v>
       </c>
       <c r="B34" t="n">
-        <v>4782</v>
+        <v>58131</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,27 +3969,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>103023</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3988,13 +4002,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>673107</v>
+        <v>673118</v>
       </c>
       <c r="R34" t="n">
-        <v>6556321</v>
+        <v>6556347</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4024,11 +4038,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4055,54 +4064,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134876582</v>
+        <v>135109471</v>
       </c>
       <c r="B35" t="n">
-        <v>58136</v>
+        <v>58131</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>673118</v>
+        <v>673071</v>
       </c>
       <c r="R35" t="n">
-        <v>6556347</v>
+        <v>6556479</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,12 +4137,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett par med flera ungar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4161,10 +4174,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134876782</v>
+        <v>134962597</v>
       </c>
       <c r="B36" t="n">
-        <v>58131</v>
+        <v>5201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4172,16 +4185,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103023</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4189,29 +4202,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>673118</v>
+        <v>673158</v>
       </c>
       <c r="R36" t="n">
-        <v>6556347</v>
+        <v>6556244</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4249,6 +4262,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4267,10 +4281,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135109471</v>
+        <v>135106795</v>
       </c>
       <c r="B37" t="n">
-        <v>58131</v>
+        <v>5201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4278,16 +4292,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103023</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4296,27 +4310,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ängshagen, Ängshagen, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>673071</v>
+        <v>673082</v>
       </c>
       <c r="R37" t="n">
-        <v>6556479</v>
+        <v>6556254</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4343,14 +4354,19 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ett par med flera ungar.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4365,22 +4381,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134873311</v>
+        <v>135111905</v>
       </c>
       <c r="B38" t="n">
-        <v>5201</v>
+        <v>8460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4388,39 +4404,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mensättraskogen, Ådalen, Srm</t>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673158</v>
+        <v>672990</v>
       </c>
       <c r="R38" t="n">
-        <v>6556244</v>
+        <v>6556541</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,12 +4463,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4479,10 +4495,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135106795</v>
+        <v>135106133</v>
       </c>
       <c r="B39" t="n">
-        <v>5201</v>
+        <v>8449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,42 +4506,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ängshagen, Ängshagen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>673082</v>
+        <v>673112</v>
       </c>
       <c r="R39" t="n">
-        <v>6556254</v>
+        <v>6556248</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4552,19 +4568,9 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4579,22 +4585,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135111905</v>
+        <v>135114337</v>
       </c>
       <c r="B40" t="n">
-        <v>8460</v>
+        <v>58839</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4602,39 +4608,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>208249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672990</v>
+        <v>673007</v>
       </c>
       <c r="R40" t="n">
-        <v>6556541</v>
+        <v>6556457</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4675,28 +4685,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135106133</v>
+        <v>134877169</v>
       </c>
       <c r="B41" t="n">
-        <v>8449</v>
+        <v>99112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4704,42 +4715,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>673112</v>
+        <v>673051</v>
       </c>
       <c r="R41" t="n">
-        <v>6556248</v>
+        <v>6556425</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4763,12 +4769,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4795,57 +4801,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135114337</v>
+        <v>134877712</v>
       </c>
       <c r="B42" t="n">
-        <v>58839</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ålsta, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>673007</v>
+        <v>673077</v>
       </c>
       <c r="R42" t="n">
-        <v>6556457</v>
+        <v>6556440</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4869,12 +4875,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4883,67 +4889,75 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134877169</v>
+        <v>134877853</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673051</v>
+        <v>673077</v>
       </c>
       <c r="R43" t="n">
-        <v>6556425</v>
+        <v>6556446</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4999,7 +5013,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134877712</v>
+        <v>135113719</v>
       </c>
       <c r="B44" t="n">
         <v>99195</v>
@@ -5029,27 +5043,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>673077</v>
+        <v>673027</v>
       </c>
       <c r="R44" t="n">
-        <v>6556440</v>
+        <v>6556383</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5073,12 +5086,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 15 plantor.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5087,238 +5105,22 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>134877853</v>
-      </c>
-      <c r="B45" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Ådalen, Ådalen, Srm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>673077</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6556446</v>
-      </c>
-      <c r="S45" t="n">
-        <v>8</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Västerhaninge</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>135113719</v>
-      </c>
-      <c r="B46" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Ålsta, Srm</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>673027</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6556383</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Västerhaninge</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ca 15 plantor.</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24801-2026 artfynd.xlsx
+++ b/artfynd/A 24801-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134875351</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135110592</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135110861</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135106253</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135106451</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135106958</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108141</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135110495</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135111384</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113394</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113440</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135114482</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135106078</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135111442</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2201,6 +2276,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134873997</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134875838</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135110590</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135111223</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135107587</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134874101</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135107231</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2905,6 +3015,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135109852</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3012,6 +3127,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135110213</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3119,6 +3239,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134875457</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3226,6 +3351,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113520</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135107091</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3430,6 +3565,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135109941</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3532,6 +3672,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134879122</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3644,6 +3789,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135114115</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3746,6 +3896,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134875172</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3848,6 +4003,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134877363</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3955,6 +4115,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134878316</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4061,6 +4226,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134876782</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4171,6 +4341,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135109471</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4278,6 +4453,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962597</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4390,6 +4570,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135106795</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4492,6 +4677,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135111905</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4594,6 +4784,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135106133</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4701,6 +4896,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135114337</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4798,6 +4998,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134877169</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4904,6 +5109,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134877712</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5010,6 +5220,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134877853</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5121,8 +5336,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113719</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24801-2026 artfynd.xlsx
+++ b/artfynd/A 24801-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135110592</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135110861</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135106253</v>
       </c>
       <c r="B5" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135106451</v>
       </c>
       <c r="B6" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135106958</v>
       </c>
       <c r="B7" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135108141</v>
       </c>
       <c r="B8" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>135110495</v>
       </c>
       <c r="B9" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135111384</v>
       </c>
       <c r="B10" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>135113394</v>
       </c>
       <c r="B11" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135113440</v>
       </c>
       <c r="B12" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135114482</v>
       </c>
       <c r="B13" t="n">
-        <v>96783</v>
+        <v>96827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>135106078</v>
       </c>
       <c r="B14" t="n">
-        <v>96533</v>
+        <v>96577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135111442</v>
       </c>
       <c r="B15" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135110590</v>
       </c>
       <c r="B18" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>135111223</v>
       </c>
       <c r="B19" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>135107587</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135107231</v>
       </c>
       <c r="B22" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>135109852</v>
       </c>
       <c r="B23" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135110213</v>
       </c>
       <c r="B24" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>135113520</v>
       </c>
       <c r="B26" t="n">
-        <v>56915</v>
+        <v>56920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135114115</v>
       </c>
       <c r="B30" t="n">
-        <v>44182</v>
+        <v>44187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135109471</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>135111905</v>
       </c>
       <c r="B38" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>135106133</v>
       </c>
       <c r="B39" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>135114337</v>
       </c>
       <c r="B40" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135113719</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 24801-2026 artfynd.xlsx
+++ b/artfynd/A 24801-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135110592</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135110861</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135106253</v>
       </c>
       <c r="B5" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135106451</v>
       </c>
       <c r="B6" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135106958</v>
       </c>
       <c r="B7" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135108141</v>
       </c>
       <c r="B8" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>135110495</v>
       </c>
       <c r="B9" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135111384</v>
       </c>
       <c r="B10" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>135113394</v>
       </c>
       <c r="B11" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135113440</v>
       </c>
       <c r="B12" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135114482</v>
       </c>
       <c r="B13" t="n">
-        <v>96827</v>
+        <v>96854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>135106078</v>
       </c>
       <c r="B14" t="n">
-        <v>96577</v>
+        <v>96604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135111442</v>
       </c>
       <c r="B15" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135110590</v>
       </c>
       <c r="B18" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>135111223</v>
       </c>
       <c r="B19" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>135107587</v>
       </c>
       <c r="B20" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135107231</v>
       </c>
       <c r="B22" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>135109852</v>
       </c>
       <c r="B23" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>135110213</v>
       </c>
       <c r="B24" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135113719</v>
       </c>
       <c r="B44" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 24801-2026 artfynd.xlsx
+++ b/artfynd/A 24801-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4234,10 +4234,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134962597</v>
+        <v>135109471</v>
       </c>
       <c r="B35" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4245,16 +4245,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4263,25 +4263,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ådalen, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>673158</v>
+        <v>673071</v>
       </c>
       <c r="R35" t="n">
-        <v>6556244</v>
+        <v>6556479</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4308,12 +4307,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett par med flera ungar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4322,7 +4326,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4340,13 +4343,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134962597</t>
+          <t>https://artportalen.se/Sighting/135109471</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135106795</v>
+        <v>134962597</v>
       </c>
       <c r="B36" t="n">
         <v>5201</v>
@@ -4375,24 +4378,28 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ängshagen, Ängshagen, Srm</t>
+          <t>Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>673082</v>
+        <v>673158</v>
       </c>
       <c r="R36" t="n">
-        <v>6556254</v>
+        <v>6556244</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4416,22 +4423,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,33 +4437,34 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135106795</t>
+          <t>https://artportalen.se/Sighting/134962597</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135111905</v>
+        <v>135106795</v>
       </c>
       <c r="B37" t="n">
-        <v>8461</v>
+        <v>5201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,42 +4472,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
+          <t>Ängshagen, Ängshagen, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672990</v>
+        <v>673082</v>
       </c>
       <c r="R37" t="n">
-        <v>6556541</v>
+        <v>6556254</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4536,9 +4534,19 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4553,27 +4561,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135111905</t>
+          <t>https://artportalen.se/Sighting/135106795</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135106133</v>
+        <v>135111905</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>8461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,21 +4589,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4606,17 +4614,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Trädgårdsstugan, Trädgårdsstugan, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>673112</v>
+        <v>672990</v>
       </c>
       <c r="R38" t="n">
-        <v>6556248</v>
+        <v>6556541</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4671,16 +4679,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135106133</t>
+          <t>https://artportalen.se/Sighting/135111905</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135114337</v>
+        <v>135106133</v>
       </c>
       <c r="B39" t="n">
-        <v>58844</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,46 +4696,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208249</v>
+        <v>106554</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ålsta, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>673007</v>
+        <v>673112</v>
       </c>
       <c r="R39" t="n">
-        <v>6556457</v>
+        <v>6556248</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4765,34 +4769,33 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135114337</t>
+          <t>https://artportalen.se/Sighting/135106133</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134877169</v>
+        <v>135114337</v>
       </c>
       <c r="B40" t="n">
-        <v>99112</v>
+        <v>58844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,37 +4803,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ådalen, Ådalen, Srm</t>
+          <t>Ålsta, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>673051</v>
+        <v>673007</v>
       </c>
       <c r="R40" t="n">
-        <v>6556425</v>
+        <v>6556457</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4854,12 +4866,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4868,77 +4880,69 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134877169</t>
+          <t>https://artportalen.se/Sighting/135114337</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134877712</v>
+        <v>134877169</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>673077</v>
+        <v>673051</v>
       </c>
       <c r="R41" t="n">
-        <v>6556440</v>
+        <v>6556425</v>
       </c>
       <c r="S41" t="n">
         <v>7</v>
@@ -4996,13 +5000,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134877712</t>
+          <t>https://artportalen.se/Sighting/134877169</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134877853</v>
+        <v>134877712</v>
       </c>
       <c r="B42" t="n">
         <v>99195</v>
@@ -5037,7 +5041,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5049,10 +5053,10 @@
         <v>673077</v>
       </c>
       <c r="R42" t="n">
-        <v>6556446</v>
+        <v>6556440</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5107,16 +5111,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134877853</t>
+          <t>https://artportalen.se/Sighting/134877712</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135113719</v>
+        <v>134877853</v>
       </c>
       <c r="B43" t="n">
-        <v>99269</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5143,26 +5147,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ålsta, Srm</t>
+          <t>Ådalen, Ådalen, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673027</v>
+        <v>673077</v>
       </c>
       <c r="R43" t="n">
-        <v>6556383</v>
+        <v>6556446</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5186,17 +5191,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ca 15 plantor.</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5205,23 +5205,138 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134877853</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135113719</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ålsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>673027</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6556383</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Västerhaninge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 15 plantor.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135113719</t>
         </is>
@@ -5271,6 +5386,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
